--- a/Test Results/Excel/Summary_Report.xlsx
+++ b/Test Results/Excel/Summary_Report.xlsx
@@ -478,14 +478,14 @@
         <v>470</v>
       </c>
       <c r="B2" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>99.36%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
